--- a/tabtools/demo/demo_desctab.xlsx
+++ b/tabtools/demo/demo_desctab.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="201" uniqueCount="75">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="201" uniqueCount="76">
   <si>
     <t>Table X. Cardiovascular Events by Education and Treatment</t>
   </si>
@@ -86,7 +86,10 @@
     <t>5,249 / 15,000 (35.0%)</t>
   </si>
   <si>
-    <t>Cells show events / N (%).</t>
+    <t>Cells show events / N (%). Statistics are generated by Stata table and formatted by desctab.</t>
+  </si>
+  <si>
+    <t>Cells show events / N (%). Shading is explicitly requested with headershade and zebra.</t>
   </si>
   <si>
     <t>Table X. Descriptive Characteristics by Treatment</t>
@@ -122,7 +125,7 @@
     <t>6.1 (6.0)</t>
   </si>
   <si>
-    <t>Cells show mean (SD).</t>
+    <t>Cells show mean (SD) with statistic-specific formats.</t>
   </si>
   <si>
     <t>Table X. CRP by Treatment</t>
@@ -143,7 +146,7 @@
     <t>4.4 (2.6-7.6)</t>
   </si>
   <si>
-    <t>Cells show median (p25-p75).</t>
+    <t>Cells show median (p25-p75), composed from table percentile statistics.</t>
   </si>
   <si>
     <t>Table X. Age by Education and Treatment</t>
@@ -11266,7 +11269,7 @@
     </row>
     <row r="7">
       <c r="B7" s="210" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C7" s="101"/>
       <c r="D7" s="101"/>
@@ -11294,7 +11297,7 @@
   <sheetData>
     <row r="1" s="216" customFormat="true" ht="30" customHeight="true">
       <c r="A1" s="250" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B1" s="242" t="s">
         <v>1</v>
@@ -11331,16 +11334,16 @@
         <v>1</v>
       </c>
       <c r="B3" s="279" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C3" s="286" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D3" s="287" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E3" s="288" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="4">
@@ -11348,16 +11351,16 @@
         <v>1</v>
       </c>
       <c r="B4" s="280" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C4" s="289" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D4" s="290" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E4" s="291" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="5">
@@ -11365,21 +11368,21 @@
         <v>1</v>
       </c>
       <c r="B5" s="281" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C5" s="292" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D5" s="293" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E5" s="294" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="6">
       <c r="B6" s="297" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C6" s="212"/>
       <c r="D6" s="212"/>
@@ -11405,7 +11408,7 @@
   <sheetData>
     <row r="1" s="301" customFormat="true" ht="30" customHeight="true">
       <c r="A1" s="323" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B1" s="317" t="s">
         <v>1</v>
@@ -11419,10 +11422,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="341" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C2" s="337" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
     </row>
     <row r="3">
@@ -11430,10 +11433,10 @@
         <v>1</v>
       </c>
       <c r="B3" s="342" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C3" s="345" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
     </row>
     <row r="4">
@@ -11441,10 +11444,10 @@
         <v>1</v>
       </c>
       <c r="B4" s="343" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C4" s="346" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
     </row>
     <row r="5">
@@ -11455,12 +11458,12 @@
         <v>6</v>
       </c>
       <c r="C5" s="347" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
     </row>
     <row r="6">
       <c r="B6" s="350" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C6" s="299"/>
     </row>
@@ -11492,7 +11495,7 @@
   <sheetData>
     <row r="1" s="362" customFormat="true" ht="30" customHeight="true">
       <c r="A1" s="454" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B1" s="440" t="s">
         <v>1</v>
@@ -11568,31 +11571,31 @@
         <v>1</v>
       </c>
       <c r="C3" s="506" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="D3" s="507" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="E3" s="544" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="F3" s="509" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="G3" s="510" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="H3" s="550" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="I3" s="512" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="J3" s="513" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="K3" s="532" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
     </row>
     <row r="4">
@@ -11603,31 +11606,31 @@
         <v>3</v>
       </c>
       <c r="C4" s="555" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D4" s="556" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="E4" s="557" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="F4" s="558" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G4" s="559" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="H4" s="560" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="I4" s="561" t="s">
+        <v>65</v>
+      </c>
+      <c r="J4" s="562" t="s">
+        <v>51</v>
+      </c>
+      <c r="K4" s="563" t="s">
         <v>64</v>
-      </c>
-      <c r="J4" s="562" t="s">
-        <v>50</v>
-      </c>
-      <c r="K4" s="563" t="s">
-        <v>63</v>
       </c>
     </row>
     <row r="5">
@@ -11638,31 +11641,31 @@
         <v>4</v>
       </c>
       <c r="C5" s="564" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="D5" s="565" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="E5" s="566" t="s">
+        <v>56</v>
+      </c>
+      <c r="F5" s="567" t="s">
+        <v>58</v>
+      </c>
+      <c r="G5" s="568" t="s">
+        <v>62</v>
+      </c>
+      <c r="H5" s="569" t="s">
+        <v>64</v>
+      </c>
+      <c r="I5" s="570" t="s">
+        <v>66</v>
+      </c>
+      <c r="J5" s="571" t="s">
+        <v>51</v>
+      </c>
+      <c r="K5" s="572" t="s">
         <v>55</v>
-      </c>
-      <c r="F5" s="567" t="s">
-        <v>57</v>
-      </c>
-      <c r="G5" s="568" t="s">
-        <v>61</v>
-      </c>
-      <c r="H5" s="569" t="s">
-        <v>63</v>
-      </c>
-      <c r="I5" s="570" t="s">
-        <v>65</v>
-      </c>
-      <c r="J5" s="571" t="s">
-        <v>50</v>
-      </c>
-      <c r="K5" s="572" t="s">
-        <v>54</v>
       </c>
     </row>
     <row r="6">
@@ -11673,31 +11676,31 @@
         <v>5</v>
       </c>
       <c r="C6" s="573" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="D6" s="574" t="s">
+        <v>52</v>
+      </c>
+      <c r="E6" s="575" t="s">
+        <v>55</v>
+      </c>
+      <c r="F6" s="576" t="s">
+        <v>59</v>
+      </c>
+      <c r="G6" s="577" t="s">
         <v>51</v>
       </c>
-      <c r="E6" s="575" t="s">
-        <v>54</v>
-      </c>
-      <c r="F6" s="576" t="s">
-        <v>58</v>
-      </c>
-      <c r="G6" s="577" t="s">
-        <v>50</v>
-      </c>
       <c r="H6" s="578" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="I6" s="579" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="J6" s="580" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="K6" s="581" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="7">
@@ -11708,36 +11711,36 @@
         <v>6</v>
       </c>
       <c r="C7" s="582" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="D7" s="583" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="E7" s="584" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="F7" s="585" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="G7" s="586" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="H7" s="587" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="I7" s="588" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="J7" s="589" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="K7" s="590" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="8">
       <c r="B8" s="593" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="C8" s="352"/>
       <c r="D8" s="352"/>
@@ -11773,7 +11776,7 @@
   <sheetData>
     <row r="1" s="597" customFormat="true" ht="30" customHeight="true">
       <c r="A1" s="622" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="B1" s="616" t="s">
         <v>1</v>
@@ -11790,7 +11793,7 @@
         <v>2</v>
       </c>
       <c r="C2" s="637" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
     </row>
     <row r="3">
@@ -11801,7 +11804,7 @@
         <v>3</v>
       </c>
       <c r="C3" s="647" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
     </row>
     <row r="4">
@@ -11812,7 +11815,7 @@
         <v>4</v>
       </c>
       <c r="C4" s="648" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
     </row>
     <row r="5">
@@ -11823,7 +11826,7 @@
         <v>5</v>
       </c>
       <c r="C5" s="649" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
     </row>
     <row r="6">
@@ -11834,12 +11837,12 @@
         <v>6</v>
       </c>
       <c r="C6" s="650" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
     </row>
     <row r="7">
       <c r="B7" s="653" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="C7" s="595"/>
     </row>

--- a/tabtools/demo/demo_desctab.xlsx
+++ b/tabtools/demo/demo_desctab.xlsx
@@ -12,13 +12,15 @@
     <sheet name="Median IQR" sheetId="4" r:id="rId6"/>
     <sheet name="Separate Stats" sheetId="5" r:id="rId7"/>
     <sheet name="Custom" sheetId="6" r:id="rId8"/>
+    <sheet name="Small Cells Primary" sheetId="7" r:id="rId9"/>
+    <sheet name="Small Cells Complement" sheetId="8" r:id="rId10"/>
   </sheets>
   <calcPr calcId="125725" fullCalcOnLoad="true"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="206" uniqueCount="81">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="288" uniqueCount="96">
   <si>
     <t>Foreign cars by repair record</t>
   </si>
@@ -262,12 +264,57 @@
   <si>
     <t>21 of 69 (30.4%)</t>
   </si>
+  <si>
+    <t>Small-cell suppression: primary counts only</t>
+  </si>
+  <si>
+    <t>Study group</t>
+  </si>
+  <si>
+    <t>Control</t>
+  </si>
+  <si>
+    <t>Treatment</t>
+  </si>
+  <si>
+    <t>Characteristic</t>
+  </si>
+  <si>
+    <t>Absent</t>
+  </si>
+  <si>
+    <t>Frequency</t>
+  </si>
+  <si>
+    <t>&lt;5</t>
+  </si>
+  <si>
+    <t>Present</t>
+  </si>
+  <si>
+    <t>10</t>
+  </si>
+  <si>
+    <t>Counts below 5 are shown as &lt;5; complementary cells are shown as ≥5 to prevent exact reconstruction.</t>
+  </si>
+  <si>
+    <t>Small-cell suppression: complementary protection</t>
+  </si>
+  <si>
+    <t>≥5</t>
+  </si>
+  <si>
+    <t>12</t>
+  </si>
+  <si>
+    <t>20</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
-  <fonts count="872">
+  <fonts count="1258">
     <font>
       <sz val="11"/>
       <name val="Calibri"/>
@@ -3890,6 +3937,1658 @@
     <font>
       <sz val="10"/>
       <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <name val="Arial"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <name val="Arial"/>
+      <i/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <name val="Arial"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <name val="Arial"/>
+      <i/>
     </font>
   </fonts>
   <fills count="20">
@@ -3990,7 +5689,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="634">
+  <borders count="904">
     <border>
       <left/>
       <right/>
@@ -8225,11 +9924,1829 @@
       <bottom style="thin"/>
       <diagonal style="none"/>
     </border>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="634">
+  <cellXfs count="904">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0"/>
@@ -10659,6 +14176,1050 @@
     </xf>
     <xf numFmtId="0" fontId="871" fillId="0" borderId="633" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="634" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="635" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="636" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="637" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="638" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="639" xfId="0"/>
+    <xf numFmtId="0" fontId="873" fillId="0" borderId="640" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="875" fillId="0" borderId="641" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="877" fillId="0" borderId="642" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="879" fillId="0" borderId="643" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="881" fillId="0" borderId="644" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="883" fillId="0" borderId="645" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="885" fillId="0" borderId="646" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="887" fillId="0" borderId="647" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="889" fillId="0" borderId="648" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="891" fillId="0" borderId="649" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="893" fillId="0" borderId="650" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="895" fillId="0" borderId="651" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="897" fillId="0" borderId="652" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="899" fillId="0" borderId="653" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="901" fillId="0" borderId="654" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="903" fillId="0" borderId="655" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="905" fillId="0" borderId="656" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="907" fillId="0" borderId="657" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="909" fillId="0" borderId="658" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="911" fillId="0" borderId="659" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="913" fillId="0" borderId="660" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="915" fillId="0" borderId="661" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="917" fillId="0" borderId="662" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="919" fillId="0" borderId="663" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="921" fillId="0" borderId="664" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="923" fillId="0" borderId="665" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="925" fillId="0" borderId="666" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="927" fillId="0" borderId="667" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="929" fillId="0" borderId="668" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="931" fillId="0" borderId="669" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="933" fillId="0" borderId="670" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="935" fillId="0" borderId="671" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="937" fillId="0" borderId="672" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="939" fillId="0" borderId="673" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="941" fillId="0" borderId="674" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="943" fillId="0" borderId="675" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="945" fillId="0" borderId="676" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="947" fillId="0" borderId="677" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="949" fillId="0" borderId="678" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="951" fillId="0" borderId="679" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="953" fillId="0" borderId="680" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="955" fillId="0" borderId="681" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="957" fillId="0" borderId="682" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="959" fillId="0" borderId="683" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="961" fillId="0" borderId="684" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="962" fillId="0" borderId="685" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="963" fillId="0" borderId="686" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="964" fillId="0" borderId="687" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="966" fillId="0" borderId="688" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="968" fillId="0" borderId="689" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="970" fillId="0" borderId="690" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="972" fillId="0" borderId="691" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="974" fillId="0" borderId="692" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="976" fillId="0" borderId="693" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="978" fillId="0" borderId="694" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="980" fillId="0" borderId="695" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="982" fillId="0" borderId="696" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="984" fillId="0" borderId="697" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="986" fillId="0" borderId="698" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="988" fillId="0" borderId="699" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="990" fillId="0" borderId="700" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="992" fillId="0" borderId="701" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="994" fillId="0" borderId="702" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="996" fillId="0" borderId="703" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="998" fillId="0" borderId="704" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="999" fillId="0" borderId="705" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1000" fillId="0" borderId="706" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1001" fillId="0" borderId="707" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1002" fillId="0" borderId="708" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1003" fillId="0" borderId="709" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1004" fillId="0" borderId="710" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1005" fillId="0" borderId="711" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1006" fillId="0" borderId="712" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1007" fillId="0" borderId="713" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1008" fillId="0" borderId="714" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1009" fillId="0" borderId="715" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1010" fillId="0" borderId="716" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1011" fillId="0" borderId="717" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1012" fillId="0" borderId="718" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1013" fillId="0" borderId="719" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1014" fillId="0" borderId="720" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1015" fillId="0" borderId="721" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1016" fillId="0" borderId="722" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1017" fillId="0" borderId="723" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1018" fillId="0" borderId="724" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1019" fillId="0" borderId="725" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1020" fillId="0" borderId="726" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1021" fillId="0" borderId="727" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1022" fillId="0" borderId="728" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1023" fillId="0" borderId="729" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1024" fillId="0" borderId="730" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1025" fillId="0" borderId="731" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1026" fillId="0" borderId="732" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1027" fillId="0" borderId="733" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1028" fillId="0" borderId="734" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1029" fillId="0" borderId="735" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1030" fillId="0" borderId="736" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1031" fillId="0" borderId="737" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1032" fillId="0" borderId="738" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1033" fillId="0" borderId="739" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1034" fillId="0" borderId="740" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1035" fillId="0" borderId="741" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1036" fillId="0" borderId="742" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1037" fillId="0" borderId="743" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1038" fillId="0" borderId="744" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1039" fillId="0" borderId="745" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1040" fillId="0" borderId="746" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1041" fillId="0" borderId="747" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1042" fillId="0" borderId="748" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1043" fillId="0" borderId="749" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1044" fillId="0" borderId="750" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1045" fillId="0" borderId="751" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1046" fillId="0" borderId="752" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1047" fillId="0" borderId="753" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1048" fillId="0" borderId="754" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1049" fillId="0" borderId="755" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1050" fillId="0" borderId="756" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1051" fillId="0" borderId="757" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1052" fillId="0" borderId="758" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1053" fillId="0" borderId="759" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1054" fillId="0" borderId="760" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1055" fillId="0" borderId="761" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1056" fillId="0" borderId="762" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1057" fillId="0" borderId="763" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1058" fillId="0" borderId="764" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1059" fillId="0" borderId="765" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1060" fillId="0" borderId="766" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1062" fillId="0" borderId="767" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1064" fillId="0" borderId="768" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="769" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="770" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="771" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="772" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="773" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="774" xfId="0"/>
+    <xf numFmtId="0" fontId="1066" fillId="0" borderId="775" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1068" fillId="0" borderId="776" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1070" fillId="0" borderId="777" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1072" fillId="0" borderId="778" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1074" fillId="0" borderId="779" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1076" fillId="0" borderId="780" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1078" fillId="0" borderId="781" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1080" fillId="0" borderId="782" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1082" fillId="0" borderId="783" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1084" fillId="0" borderId="784" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1086" fillId="0" borderId="785" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1088" fillId="0" borderId="786" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1090" fillId="0" borderId="787" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1092" fillId="0" borderId="788" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1094" fillId="0" borderId="789" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1096" fillId="0" borderId="790" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1098" fillId="0" borderId="791" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1100" fillId="0" borderId="792" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1102" fillId="0" borderId="793" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1104" fillId="0" borderId="794" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1106" fillId="0" borderId="795" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1108" fillId="0" borderId="796" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1110" fillId="0" borderId="797" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1112" fillId="0" borderId="798" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1114" fillId="0" borderId="799" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1116" fillId="0" borderId="800" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1118" fillId="0" borderId="801" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1120" fillId="0" borderId="802" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1122" fillId="0" borderId="803" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1124" fillId="0" borderId="804" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1126" fillId="0" borderId="805" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1128" fillId="0" borderId="806" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1130" fillId="0" borderId="807" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1132" fillId="0" borderId="808" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1134" fillId="0" borderId="809" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1136" fillId="0" borderId="810" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1138" fillId="0" borderId="811" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1140" fillId="0" borderId="812" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1142" fillId="0" borderId="813" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1144" fillId="0" borderId="814" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1146" fillId="0" borderId="815" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1148" fillId="0" borderId="816" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1150" fillId="0" borderId="817" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1152" fillId="0" borderId="818" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1154" fillId="0" borderId="819" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1155" fillId="0" borderId="820" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1156" fillId="0" borderId="821" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1157" fillId="0" borderId="822" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1159" fillId="0" borderId="823" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1161" fillId="0" borderId="824" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1163" fillId="0" borderId="825" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1165" fillId="0" borderId="826" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1167" fillId="0" borderId="827" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1169" fillId="0" borderId="828" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1171" fillId="0" borderId="829" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1173" fillId="0" borderId="830" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1175" fillId="0" borderId="831" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1177" fillId="0" borderId="832" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1179" fillId="0" borderId="833" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1181" fillId="0" borderId="834" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1183" fillId="0" borderId="835" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1185" fillId="0" borderId="836" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1187" fillId="0" borderId="837" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1189" fillId="0" borderId="838" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1191" fillId="0" borderId="839" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1192" fillId="0" borderId="840" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1193" fillId="0" borderId="841" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1194" fillId="0" borderId="842" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1195" fillId="0" borderId="843" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1196" fillId="0" borderId="844" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1197" fillId="0" borderId="845" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1198" fillId="0" borderId="846" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1199" fillId="0" borderId="847" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1200" fillId="0" borderId="848" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1201" fillId="0" borderId="849" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1202" fillId="0" borderId="850" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1203" fillId="0" borderId="851" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1204" fillId="0" borderId="852" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1205" fillId="0" borderId="853" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1206" fillId="0" borderId="854" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1207" fillId="0" borderId="855" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1208" fillId="0" borderId="856" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1209" fillId="0" borderId="857" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1210" fillId="0" borderId="858" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1211" fillId="0" borderId="859" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1212" fillId="0" borderId="860" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1213" fillId="0" borderId="861" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1214" fillId="0" borderId="862" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1215" fillId="0" borderId="863" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1216" fillId="0" borderId="864" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1217" fillId="0" borderId="865" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1218" fillId="0" borderId="866" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1219" fillId="0" borderId="867" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1220" fillId="0" borderId="868" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1221" fillId="0" borderId="869" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1222" fillId="0" borderId="870" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1223" fillId="0" borderId="871" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1224" fillId="0" borderId="872" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1225" fillId="0" borderId="873" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1226" fillId="0" borderId="874" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1227" fillId="0" borderId="875" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1228" fillId="0" borderId="876" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1229" fillId="0" borderId="877" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1230" fillId="0" borderId="878" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1231" fillId="0" borderId="879" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1232" fillId="0" borderId="880" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1233" fillId="0" borderId="881" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1234" fillId="0" borderId="882" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1235" fillId="0" borderId="883" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1236" fillId="0" borderId="884" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1237" fillId="0" borderId="885" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1238" fillId="0" borderId="886" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1239" fillId="0" borderId="887" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1240" fillId="0" borderId="888" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1241" fillId="0" borderId="889" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1242" fillId="0" borderId="890" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1243" fillId="0" borderId="891" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1244" fillId="0" borderId="892" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1245" fillId="0" borderId="893" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1246" fillId="0" borderId="894" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1247" fillId="0" borderId="895" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1248" fillId="0" borderId="896" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1249" fillId="0" borderId="897" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1250" fillId="0" borderId="898" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1251" fillId="0" borderId="899" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1252" fillId="0" borderId="900" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1253" fillId="0" borderId="901" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1255" fillId="0" borderId="902" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1257" fillId="0" borderId="903" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
   </cellXfs>
@@ -11484,4 +16045,332 @@
     <mergeCell ref="A1:C1"/>
   </mergeCells>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:E9"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="1.7109375" style="634" customWidth="true"/>
+    <col min="2" max="2" width="13.7109375" style="635" customWidth="true"/>
+    <col min="3" max="3" width="16.7109375" style="636" customWidth="true"/>
+    <col min="4" max="4" width="16.7109375" style="637" customWidth="true"/>
+    <col min="5" max="5" width="16.7109375" style="638" customWidth="true"/>
+  </cols>
+  <sheetData>
+    <row r="1" s="639" customFormat="true" ht="30" customHeight="true">
+      <c r="A1" s="688" t="s">
+        <v>81</v>
+      </c>
+      <c r="B1" s="680" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="680" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" s="680" t="s">
+        <v>1</v>
+      </c>
+      <c r="E1" s="680" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="645" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2" s="743" t="s">
+        <v>1</v>
+      </c>
+      <c r="C2" s="718" t="s">
+        <v>85</v>
+      </c>
+      <c r="D2" s="750" t="s">
+        <v>85</v>
+      </c>
+      <c r="E2" s="736" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="650" t="s">
+        <v>1</v>
+      </c>
+      <c r="B3" s="744" t="s">
+        <v>1</v>
+      </c>
+      <c r="C3" s="708" t="s">
+        <v>86</v>
+      </c>
+      <c r="D3" s="751" t="s">
+        <v>89</v>
+      </c>
+      <c r="E3" s="737" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="655" t="s">
+        <v>1</v>
+      </c>
+      <c r="B4" s="745" t="s">
+        <v>1</v>
+      </c>
+      <c r="C4" s="711" t="s">
+        <v>87</v>
+      </c>
+      <c r="D4" s="752" t="s">
+        <v>87</v>
+      </c>
+      <c r="E4" s="738" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="660" t="s">
+        <v>1</v>
+      </c>
+      <c r="B5" s="746" t="s">
+        <v>82</v>
+      </c>
+      <c r="C5" s="722" t="s">
+        <v>1</v>
+      </c>
+      <c r="D5" s="753" t="s">
+        <v>1</v>
+      </c>
+      <c r="E5" s="739" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="665" t="s">
+        <v>1</v>
+      </c>
+      <c r="B6" s="747" t="s">
+        <v>83</v>
+      </c>
+      <c r="C6" s="757" t="s">
+        <v>88</v>
+      </c>
+      <c r="D6" s="758" t="s">
+        <v>88</v>
+      </c>
+      <c r="E6" s="759" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="670" t="s">
+        <v>1</v>
+      </c>
+      <c r="B7" s="748" t="s">
+        <v>84</v>
+      </c>
+      <c r="C7" s="760" t="s">
+        <v>88</v>
+      </c>
+      <c r="D7" s="761" t="s">
+        <v>88</v>
+      </c>
+      <c r="E7" s="762" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="675" t="s">
+        <v>1</v>
+      </c>
+      <c r="B8" s="749" t="s">
+        <v>8</v>
+      </c>
+      <c r="C8" s="763" t="s">
+        <v>7</v>
+      </c>
+      <c r="D8" s="764" t="s">
+        <v>7</v>
+      </c>
+      <c r="E8" s="765" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="B9" s="768" t="s">
+        <v>91</v>
+      </c>
+      <c r="C9" s="0"/>
+      <c r="D9" s="0"/>
+      <c r="E9" s="0"/>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A1:E1"/>
+    <mergeCell ref="B9:E9"/>
+  </mergeCells>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:E9"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="1.7109375" style="769" customWidth="true"/>
+    <col min="2" max="2" width="13.7109375" style="770" customWidth="true"/>
+    <col min="3" max="3" width="16.7109375" style="771" customWidth="true"/>
+    <col min="4" max="4" width="16.7109375" style="772" customWidth="true"/>
+    <col min="5" max="5" width="16.7109375" style="773" customWidth="true"/>
+  </cols>
+  <sheetData>
+    <row r="1" s="774" customFormat="true" ht="30" customHeight="true">
+      <c r="A1" s="823" t="s">
+        <v>92</v>
+      </c>
+      <c r="B1" s="815" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="815" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" s="815" t="s">
+        <v>1</v>
+      </c>
+      <c r="E1" s="815" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="780" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2" s="878" t="s">
+        <v>1</v>
+      </c>
+      <c r="C2" s="853" t="s">
+        <v>85</v>
+      </c>
+      <c r="D2" s="885" t="s">
+        <v>85</v>
+      </c>
+      <c r="E2" s="871" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="785" t="s">
+        <v>1</v>
+      </c>
+      <c r="B3" s="879" t="s">
+        <v>1</v>
+      </c>
+      <c r="C3" s="843" t="s">
+        <v>86</v>
+      </c>
+      <c r="D3" s="886" t="s">
+        <v>89</v>
+      </c>
+      <c r="E3" s="872" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="790" t="s">
+        <v>1</v>
+      </c>
+      <c r="B4" s="880" t="s">
+        <v>1</v>
+      </c>
+      <c r="C4" s="846" t="s">
+        <v>87</v>
+      </c>
+      <c r="D4" s="887" t="s">
+        <v>87</v>
+      </c>
+      <c r="E4" s="873" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="795" t="s">
+        <v>1</v>
+      </c>
+      <c r="B5" s="881" t="s">
+        <v>82</v>
+      </c>
+      <c r="C5" s="857" t="s">
+        <v>1</v>
+      </c>
+      <c r="D5" s="888" t="s">
+        <v>1</v>
+      </c>
+      <c r="E5" s="874" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="800" t="s">
+        <v>1</v>
+      </c>
+      <c r="B6" s="882" t="s">
+        <v>83</v>
+      </c>
+      <c r="C6" s="892" t="s">
+        <v>88</v>
+      </c>
+      <c r="D6" s="893" t="s">
+        <v>93</v>
+      </c>
+      <c r="E6" s="894" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="805" t="s">
+        <v>1</v>
+      </c>
+      <c r="B7" s="883" t="s">
+        <v>84</v>
+      </c>
+      <c r="C7" s="895" t="s">
+        <v>93</v>
+      </c>
+      <c r="D7" s="896" t="s">
+        <v>88</v>
+      </c>
+      <c r="E7" s="897" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="810" t="s">
+        <v>1</v>
+      </c>
+      <c r="B8" s="884" t="s">
+        <v>8</v>
+      </c>
+      <c r="C8" s="898" t="s">
+        <v>35</v>
+      </c>
+      <c r="D8" s="899" t="s">
+        <v>94</v>
+      </c>
+      <c r="E8" s="900" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="B9" s="903" t="s">
+        <v>91</v>
+      </c>
+      <c r="C9" s="0"/>
+      <c r="D9" s="0"/>
+      <c r="E9" s="0"/>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A1:E1"/>
+    <mergeCell ref="B9:E9"/>
+  </mergeCells>
+</worksheet>
 </file>
--- a/tabtools/demo/demo_desctab.xlsx
+++ b/tabtools/demo/demo_desctab.xlsx
@@ -14,13 +14,14 @@
     <sheet name="Custom" sheetId="6" r:id="rId8"/>
     <sheet name="Small Cells Primary" sheetId="7" r:id="rId9"/>
     <sheet name="Small Cells Complement" sheetId="8" r:id="rId10"/>
+    <sheet name="Small Cells Binary" sheetId="9" r:id="rId11"/>
   </sheets>
   <calcPr calcId="125725" fullCalcOnLoad="true"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="288" uniqueCount="96">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="329" uniqueCount="103">
   <si>
     <t>Foreign cars by repair record</t>
   </si>
@@ -309,12 +310,33 @@
   <si>
     <t>20</t>
   </si>
+  <si>
+    <t>Small-cell suppression: binary variable</t>
+  </si>
+  <si>
+    <t>Rare adverse event</t>
+  </si>
+  <si>
+    <t>No</t>
+  </si>
+  <si>
+    <t>95</t>
+  </si>
+  <si>
+    <t>Yes</t>
+  </si>
+  <si>
+    <t>50</t>
+  </si>
+  <si>
+    <t>100</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
-  <fonts count="1258">
+  <fonts count="1451">
     <font>
       <sz val="11"/>
       <name val="Calibri"/>
@@ -3937,6 +3959,832 @@
     <font>
       <sz val="10"/>
       <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <name val="Arial"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <name val="Arial"/>
+      <i/>
     </font>
     <font>
       <sz val="11"/>
@@ -5689,7 +6537,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="904">
+  <borders count="1039">
     <border>
       <left/>
       <right/>
@@ -11742,11 +12590,920 @@
       <bottom style="none"/>
       <diagonal style="none"/>
     </border>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="904">
+  <cellXfs count="1039">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0"/>
@@ -15219,6 +16976,528 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="0" fontId="1257" fillId="0" borderId="903" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="904" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="905" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="906" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="907" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="908" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="909" xfId="0"/>
+    <xf numFmtId="0" fontId="1259" fillId="0" borderId="910" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1261" fillId="0" borderId="911" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1263" fillId="0" borderId="912" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1265" fillId="0" borderId="913" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1267" fillId="0" borderId="914" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1269" fillId="0" borderId="915" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1271" fillId="0" borderId="916" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1273" fillId="0" borderId="917" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1275" fillId="0" borderId="918" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1277" fillId="0" borderId="919" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1279" fillId="0" borderId="920" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1281" fillId="0" borderId="921" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1283" fillId="0" borderId="922" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1285" fillId="0" borderId="923" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1287" fillId="0" borderId="924" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1289" fillId="0" borderId="925" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1291" fillId="0" borderId="926" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1293" fillId="0" borderId="927" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1295" fillId="0" borderId="928" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1297" fillId="0" borderId="929" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1299" fillId="0" borderId="930" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1301" fillId="0" borderId="931" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1303" fillId="0" borderId="932" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1305" fillId="0" borderId="933" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1307" fillId="0" borderId="934" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1309" fillId="0" borderId="935" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1311" fillId="0" borderId="936" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1313" fillId="0" borderId="937" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1315" fillId="0" borderId="938" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1317" fillId="0" borderId="939" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1319" fillId="0" borderId="940" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1321" fillId="0" borderId="941" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1323" fillId="0" borderId="942" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1325" fillId="0" borderId="943" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1327" fillId="0" borderId="944" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1329" fillId="0" borderId="945" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1331" fillId="0" borderId="946" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1333" fillId="0" borderId="947" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1335" fillId="0" borderId="948" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1337" fillId="0" borderId="949" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1339" fillId="0" borderId="950" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1341" fillId="0" borderId="951" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1343" fillId="0" borderId="952" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1345" fillId="0" borderId="953" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1347" fillId="0" borderId="954" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1348" fillId="0" borderId="955" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1349" fillId="0" borderId="956" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1350" fillId="0" borderId="957" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1352" fillId="0" borderId="958" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1354" fillId="0" borderId="959" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1356" fillId="0" borderId="960" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1358" fillId="0" borderId="961" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1360" fillId="0" borderId="962" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1362" fillId="0" borderId="963" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1364" fillId="0" borderId="964" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1366" fillId="0" borderId="965" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1368" fillId="0" borderId="966" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1370" fillId="0" borderId="967" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1372" fillId="0" borderId="968" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1374" fillId="0" borderId="969" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1376" fillId="0" borderId="970" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1378" fillId="0" borderId="971" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1380" fillId="0" borderId="972" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1382" fillId="0" borderId="973" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1384" fillId="0" borderId="974" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1385" fillId="0" borderId="975" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1386" fillId="0" borderId="976" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1387" fillId="0" borderId="977" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1388" fillId="0" borderId="978" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1389" fillId="0" borderId="979" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1390" fillId="0" borderId="980" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1391" fillId="0" borderId="981" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1392" fillId="0" borderId="982" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1393" fillId="0" borderId="983" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1394" fillId="0" borderId="984" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1395" fillId="0" borderId="985" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1396" fillId="0" borderId="986" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1397" fillId="0" borderId="987" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1398" fillId="0" borderId="988" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1399" fillId="0" borderId="989" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1400" fillId="0" borderId="990" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1401" fillId="0" borderId="991" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1402" fillId="0" borderId="992" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1403" fillId="0" borderId="993" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1404" fillId="0" borderId="994" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1405" fillId="0" borderId="995" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1406" fillId="0" borderId="996" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1407" fillId="0" borderId="997" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1408" fillId="0" borderId="998" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1409" fillId="0" borderId="999" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1410" fillId="0" borderId="1000" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1411" fillId="0" borderId="1001" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1412" fillId="0" borderId="1002" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1413" fillId="0" borderId="1003" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1414" fillId="0" borderId="1004" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1415" fillId="0" borderId="1005" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1416" fillId="0" borderId="1006" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1417" fillId="0" borderId="1007" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1418" fillId="0" borderId="1008" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1419" fillId="0" borderId="1009" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1420" fillId="0" borderId="1010" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1421" fillId="0" borderId="1011" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1422" fillId="0" borderId="1012" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1423" fillId="0" borderId="1013" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1424" fillId="0" borderId="1014" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1425" fillId="0" borderId="1015" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1426" fillId="0" borderId="1016" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1427" fillId="0" borderId="1017" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1428" fillId="0" borderId="1018" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1429" fillId="0" borderId="1019" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1430" fillId="0" borderId="1020" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1431" fillId="0" borderId="1021" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1432" fillId="0" borderId="1022" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1433" fillId="0" borderId="1023" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1434" fillId="0" borderId="1024" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1435" fillId="0" borderId="1025" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1436" fillId="0" borderId="1026" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1437" fillId="0" borderId="1027" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1438" fillId="0" borderId="1028" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1439" fillId="0" borderId="1029" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1440" fillId="0" borderId="1030" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1441" fillId="0" borderId="1031" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1442" fillId="0" borderId="1032" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1443" fillId="0" borderId="1033" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1444" fillId="0" borderId="1034" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1445" fillId="0" borderId="1035" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1446" fillId="0" borderId="1036" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1448" fillId="0" borderId="1037" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1450" fillId="0" borderId="1038" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -16373,4 +18652,168 @@
     <mergeCell ref="B9:E9"/>
   </mergeCells>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:E9"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="1.7109375" style="904" customWidth="true"/>
+    <col min="2" max="2" width="13.7109375" style="905" customWidth="true"/>
+    <col min="3" max="3" width="20.7109375" style="906" customWidth="true"/>
+    <col min="4" max="4" width="20.7109375" style="907" customWidth="true"/>
+    <col min="5" max="5" width="20.7109375" style="908" customWidth="true"/>
+  </cols>
+  <sheetData>
+    <row r="1" s="909" customFormat="true" ht="30" customHeight="true">
+      <c r="A1" s="958" t="s">
+        <v>96</v>
+      </c>
+      <c r="B1" s="950" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="950" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" s="950" t="s">
+        <v>1</v>
+      </c>
+      <c r="E1" s="950" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="915" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2" s="1013" t="s">
+        <v>1</v>
+      </c>
+      <c r="C2" s="988" t="s">
+        <v>97</v>
+      </c>
+      <c r="D2" s="1020" t="s">
+        <v>97</v>
+      </c>
+      <c r="E2" s="1006" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="920" t="s">
+        <v>1</v>
+      </c>
+      <c r="B3" s="1014" t="s">
+        <v>1</v>
+      </c>
+      <c r="C3" s="978" t="s">
+        <v>98</v>
+      </c>
+      <c r="D3" s="1021" t="s">
+        <v>100</v>
+      </c>
+      <c r="E3" s="1007" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="925" t="s">
+        <v>1</v>
+      </c>
+      <c r="B4" s="1015" t="s">
+        <v>1</v>
+      </c>
+      <c r="C4" s="981" t="s">
+        <v>87</v>
+      </c>
+      <c r="D4" s="1022" t="s">
+        <v>87</v>
+      </c>
+      <c r="E4" s="1008" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="930" t="s">
+        <v>1</v>
+      </c>
+      <c r="B5" s="1016" t="s">
+        <v>82</v>
+      </c>
+      <c r="C5" s="992" t="s">
+        <v>1</v>
+      </c>
+      <c r="D5" s="1023" t="s">
+        <v>1</v>
+      </c>
+      <c r="E5" s="1009" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="935" t="s">
+        <v>1</v>
+      </c>
+      <c r="B6" s="1017" t="s">
+        <v>83</v>
+      </c>
+      <c r="C6" s="1027" t="s">
+        <v>93</v>
+      </c>
+      <c r="D6" s="1028" t="s">
+        <v>88</v>
+      </c>
+      <c r="E6" s="1029" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="940" t="s">
+        <v>1</v>
+      </c>
+      <c r="B7" s="1018" t="s">
+        <v>84</v>
+      </c>
+      <c r="C7" s="1030" t="s">
+        <v>93</v>
+      </c>
+      <c r="D7" s="1031" t="s">
+        <v>88</v>
+      </c>
+      <c r="E7" s="1032" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="945" t="s">
+        <v>1</v>
+      </c>
+      <c r="B8" s="1019" t="s">
+        <v>8</v>
+      </c>
+      <c r="C8" s="1033" t="s">
+        <v>99</v>
+      </c>
+      <c r="D8" s="1034" t="s">
+        <v>7</v>
+      </c>
+      <c r="E8" s="1035" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="B9" s="1038" t="s">
+        <v>91</v>
+      </c>
+      <c r="C9" s="0"/>
+      <c r="D9" s="0"/>
+      <c r="E9" s="0"/>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A1:E1"/>
+    <mergeCell ref="B9:E9"/>
+  </mergeCells>
+</worksheet>
 </file>
--- a/tabtools/demo/demo_desctab.xlsx
+++ b/tabtools/demo/demo_desctab.xlsx
@@ -961,8 +961,8 @@
   <cols>
     <col min="1" max="1" width="1.7109375" style="1" customWidth="true"/>
     <col min="2" max="2" width="15.7109375" style="1" customWidth="true"/>
-    <col min="3" max="3" width="14.7109375" style="1" customWidth="true"/>
-    <col min="4" max="4" width="14.7109375" style="1" customWidth="true"/>
+    <col min="3" max="3" width="13.7109375" style="1" customWidth="true"/>
+    <col min="4" max="4" width="13.7109375" style="1" customWidth="true"/>
     <col min="5" max="5" width="10.7109375" style="1" customWidth="true"/>
   </cols>
   <sheetData>
@@ -1156,8 +1156,8 @@
   <cols>
     <col min="1" max="1" width="1.7109375" style="1" customWidth="true"/>
     <col min="2" max="2" width="18.7109375" style="1" customWidth="true"/>
-    <col min="3" max="3" width="13.7109375" style="1" customWidth="true"/>
-    <col min="4" max="4" width="13.7109375" style="1" customWidth="true"/>
+    <col min="3" max="3" width="12.7109375" style="1" customWidth="true"/>
+    <col min="4" max="4" width="12.7109375" style="1" customWidth="true"/>
     <col min="5" max="5" width="10.7109375" style="1" customWidth="true"/>
   </cols>
   <sheetData>
